--- a/data/trans_dic/P29A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,74; 57,47</t>
+          <t>45,15; 57,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,42; 62,4</t>
+          <t>50,58; 61,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,76; 66,12</t>
+          <t>53,28; 65,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49,93; 64,36</t>
+          <t>50,29; 64,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,26; 34,44</t>
+          <t>22,14; 33,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,19; 40,39</t>
+          <t>28,12; 39,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 40,5</t>
+          <t>28,92; 40,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 36,02</t>
+          <t>27,21; 36,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>36,13; 44,53</t>
+          <t>35,41; 43,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,09; 49,81</t>
+          <t>41,14; 50,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,69; 52,02</t>
+          <t>43,51; 52,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,7; 49,12</t>
+          <t>40,18; 49,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,82; 47,0</t>
+          <t>38,07; 47,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,58; 62,02</t>
+          <t>52,07; 61,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,5; 56,7</t>
+          <t>47,37; 55,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,69; 55,43</t>
+          <t>44,7; 55,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 14,46</t>
+          <t>8,84; 14,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,22; 27,77</t>
+          <t>20,22; 28,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 21,46</t>
+          <t>14,75; 21,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,23; 26,11</t>
+          <t>19,53; 26,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,1; 30,17</t>
+          <t>23,99; 29,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,02; 43,83</t>
+          <t>36,73; 43,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,53; 37,69</t>
+          <t>31,11; 37,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 39,63</t>
+          <t>33,12; 39,82</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54,04; 64,73</t>
+          <t>53,9; 64,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,86; 63,84</t>
+          <t>51,51; 62,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>56,33; 66,88</t>
+          <t>57,07; 67,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52,99; 64,18</t>
+          <t>53,09; 64,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,64; 30,22</t>
+          <t>20,17; 29,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,51; 38,01</t>
+          <t>27,25; 38,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,72; 39,62</t>
+          <t>29,83; 40,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,67; 29,9</t>
+          <t>21,7; 30,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,69; 45,83</t>
+          <t>37,9; 45,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,79; 48,76</t>
+          <t>40,43; 48,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,4; 51,37</t>
+          <t>43,6; 51,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,98; 45,12</t>
+          <t>37,82; 45,05</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,64; 69,31</t>
+          <t>59,71; 70,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,77; 52,37</t>
+          <t>41,42; 52,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,63; 64,08</t>
+          <t>53,92; 64,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,03; 63,83</t>
+          <t>49,84; 63,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,69; 39,46</t>
+          <t>29,64; 39,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,0</t>
+          <t>15,01; 23,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,98; 41,29</t>
+          <t>30,57; 41,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,81; 33,26</t>
+          <t>16,5; 33,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 53,03</t>
+          <t>46,11; 53,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,78; 35,87</t>
+          <t>28,94; 36,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,49; 51,01</t>
+          <t>43,38; 50,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,79; 44,83</t>
+          <t>27,77; 44,23</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,83; 49,63</t>
+          <t>36,11; 49,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,66; 64,03</t>
+          <t>50,21; 64,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,0; 48,38</t>
+          <t>34,99; 48,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,21; 22,99</t>
+          <t>12,9; 22,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,16; 24,7</t>
+          <t>13,06; 23,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 27,87</t>
+          <t>16,51; 27,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 22,56</t>
+          <t>12,27; 22,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 6,85</t>
+          <t>2,44; 7,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,81; 34,58</t>
+          <t>25,85; 35,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,45; 43,83</t>
+          <t>34,39; 44,1</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,8; 33,34</t>
+          <t>24,77; 33,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,08</t>
+          <t>7,85; 12,88</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,75; 75,79</t>
+          <t>65,24; 76,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58,86; 71,32</t>
+          <t>59,44; 71,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,58; 75,91</t>
+          <t>64,75; 76,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,71; 66,35</t>
+          <t>55,93; 66,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,25; 44,97</t>
+          <t>33,25; 45,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,63; 35,6</t>
+          <t>24,2; 35,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,45; 43,45</t>
+          <t>31,53; 43,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,73; 42,49</t>
+          <t>32,57; 42,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,47; 58,78</t>
+          <t>50,7; 58,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42,43; 51,76</t>
+          <t>42,74; 51,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,25; 57,84</t>
+          <t>49,07; 57,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,91; 53,65</t>
+          <t>46,32; 53,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>41,25; 49,27</t>
+          <t>40,94; 49,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,74; 61,06</t>
+          <t>52,45; 60,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,19; 61,56</t>
+          <t>53,47; 61,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,0; 54,51</t>
+          <t>44,94; 55,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,88; 23,06</t>
+          <t>16,76; 22,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,9; 30,84</t>
+          <t>24,03; 31,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,74; 40,37</t>
+          <t>32,73; 40,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,66; 72,81</t>
+          <t>29,37; 73,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,58; 34,98</t>
+          <t>29,46; 34,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,7; 44,06</t>
+          <t>38,65; 44,37</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,77; 49,49</t>
+          <t>43,86; 49,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,81; 67,34</t>
+          <t>39,06; 67,92</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>60,0; 66,93</t>
+          <t>59,84; 66,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,76; 58,34</t>
+          <t>50,62; 58,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,79; 59,8</t>
+          <t>52,59; 59,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,56; 41,83</t>
+          <t>13,57; 42,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,26; 30,48</t>
+          <t>24,39; 30,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,64; 25,83</t>
+          <t>19,73; 26,17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,89; 33,44</t>
+          <t>26,8; 33,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,99; 16,63</t>
+          <t>12,01; 16,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,24; 47,2</t>
+          <t>42,34; 47,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35,45; 40,67</t>
+          <t>35,42; 40,48</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39,77; 45,02</t>
+          <t>39,91; 45,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,56; 27,57</t>
+          <t>12,9; 27,84</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53,24; 56,61</t>
+          <t>52,95; 56,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54,36; 58,09</t>
+          <t>54,31; 58,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55,41; 58,82</t>
+          <t>55,34; 58,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36,17; 49,79</t>
+          <t>34,76; 49,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,05; 25,95</t>
+          <t>23,1; 26,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,28; 27,35</t>
+          <t>24,29; 27,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,24; 32,44</t>
+          <t>29,13; 32,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,31; 40,2</t>
+          <t>23,29; 41,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,67</t>
+          <t>38,25; 40,71</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39,29; 41,71</t>
+          <t>39,16; 41,7</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42,34; 44,85</t>
+          <t>42,4; 44,83</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33,43; 42,68</t>
+          <t>33,1; 42,22</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>120286; 154506</t>
+          <t>121382; 153586</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148137; 183314</t>
+          <t>148601; 181898</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154907; 190524</t>
+          <t>153539; 188911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>155510; 200447</t>
+          <t>156628; 202056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>60437; 89498</t>
+          <t>57539; 86926</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79830; 114354</t>
+          <t>79626; 113102</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82407; 113838</t>
+          <t>81284; 112584</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78078; 104322</t>
+          <t>78805; 105927</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>191022; 235404</t>
+          <t>187223; 232070</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>237080; 287396</t>
+          <t>237372; 288520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248703; 296138</t>
+          <t>247652; 298170</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>244645; 295263</t>
+          <t>241485; 295637</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>183045; 227458</t>
+          <t>184246; 228591</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>251623; 296807</t>
+          <t>249165; 294617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>232954; 278100</t>
+          <t>232311; 274598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>225502; 286146</t>
+          <t>230715; 285870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44412; 72130</t>
+          <t>44110; 73963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>102410; 140680</t>
+          <t>102437; 142866</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75844; 110781</t>
+          <t>76169; 112459</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98938; 134307</t>
+          <t>100478; 138486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>236806; 296457</t>
+          <t>235736; 291096</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>364679; 431741</t>
+          <t>361832; 425377</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>317433; 379421</t>
+          <t>313180; 376730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>333903; 408375</t>
+          <t>341280; 410364</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>169710; 203285</t>
+          <t>169281; 203367</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>157952; 194437</t>
+          <t>156893; 191424</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166696; 197895</t>
+          <t>168888; 198973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167478; 202827</t>
+          <t>167807; 202714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68842; 100773</t>
+          <t>67258; 99598</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91089; 125822</t>
+          <t>90198; 126353</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98201; 130898</t>
+          <t>98555; 132895</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75562; 104240</t>
+          <t>75668; 104955</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>244029; 296769</t>
+          <t>245416; 294554</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>259255; 309958</t>
+          <t>257020; 307747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>271790; 321734</t>
+          <t>273092; 321298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>252465; 299942</t>
+          <t>251384; 299450</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211563; 245862</t>
+          <t>211820; 248337</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149466; 187416</t>
+          <t>148223; 186973</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>193291; 230969</t>
+          <t>194343; 231399</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>153232; 199491</t>
+          <t>155779; 199656</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110271; 146562</t>
+          <t>110103; 144909</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57151; 88396</t>
+          <t>57701; 88399</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>117226; 156228</t>
+          <t>115685; 155493</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75233; 158243</t>
+          <t>78486; 160776</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>330817; 385091</t>
+          <t>334877; 384854</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>213616; 266223</t>
+          <t>214792; 267347</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>321281; 376907</t>
+          <t>320490; 374748</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>219065; 353406</t>
+          <t>218925; 348665</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>70976; 98311</t>
+          <t>71538; 97940</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>107708; 136129</t>
+          <t>106765; 136572</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70563; 100394</t>
+          <t>72603; 101095</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23609; 41089</t>
+          <t>23058; 40705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27205; 51052</t>
+          <t>27002; 49199</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34512; 61192</t>
+          <t>36244; 60588</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26861; 49320</t>
+          <t>26829; 49220</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5223; 14285</t>
+          <t>5081; 14655</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104477; 139957</t>
+          <t>104641; 142056</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148887; 189427</t>
+          <t>148628; 190609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105687; 142056</t>
+          <t>105565; 142033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30270; 50688</t>
+          <t>30427; 49889</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>174037; 203713</t>
+          <t>175367; 204432</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>155391; 188296</t>
+          <t>156923; 187613</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>166864; 196145</t>
+          <t>167306; 196653</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149548; 178127</t>
+          <t>150145; 177563</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91800; 124154</t>
+          <t>91782; 124950</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>68207; 98574</t>
+          <t>67005; 97887</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87998; 117812</t>
+          <t>85493; 117688</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84145; 109222</t>
+          <t>83726; 108778</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>274997; 320302</t>
+          <t>276260; 321321</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>229498; 280009</t>
+          <t>231220; 278377</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>260816; 306271</t>
+          <t>259823; 306412</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>241261; 281916</t>
+          <t>243416; 283455</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>249551; 298074</t>
+          <t>247681; 299507</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>333272; 385851</t>
+          <t>331430; 385070</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>340790; 394444</t>
+          <t>342632; 394955</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>279374; 338475</t>
+          <t>279054; 343235</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106990; 146155</t>
+          <t>106197; 144864</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>163755; 211308</t>
+          <t>164624; 213725</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>223846; 276023</t>
+          <t>223801; 275906</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>250686; 615416</t>
+          <t>248222; 624290</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>366353; 433269</t>
+          <t>364903; 431173</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>509700; 580233</t>
+          <t>508986; 584383</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>579743; 655529</t>
+          <t>580950; 653802</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>568999; 987241</t>
+          <t>572588; 995784</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>443478; 494736</t>
+          <t>442313; 494858</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>371199; 426578</t>
+          <t>370140; 426544</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>393760; 446059</t>
+          <t>392310; 446307</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>116669; 388504</t>
+          <t>126052; 391844</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>189306; 237818</t>
+          <t>190344; 240019</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>156989; 206517</t>
+          <t>157750; 209241</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>217355; 270353</t>
+          <t>216647; 271026</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>85480; 118547</t>
+          <t>85630; 118234</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>641765; 717124</t>
+          <t>643290; 717220</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>542688; 622570</t>
+          <t>542170; 619588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>618109; 699833</t>
+          <t>620300; 701349</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>222597; 452552</t>
+          <t>211748; 457055</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1721081; 1830050</t>
+          <t>1711533; 1832417</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1779918; 1902363</t>
+          <t>1778373; 1900727</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1821769; 1933711</t>
+          <t>1819409; 1934282</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1248887; 1719386</t>
+          <t>1200308; 1723251</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>774438; 871859</t>
+          <t>776264; 875351</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>846381; 953364</t>
+          <t>846842; 949519</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1019800; 1131476</t>
+          <t>1016079; 1129875</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>851493; 1468125</t>
+          <t>850746; 1518369</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2521204; 2681089</t>
+          <t>2521776; 2683702</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2656385; 2820098</t>
+          <t>2647611; 2819507</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2868467; 3039082</t>
+          <t>2873027; 3037583</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2375497; 3032422</t>
+          <t>2351846; 3000156</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P29A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,15; 57,13</t>
+          <t>45,74; 56,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,58; 61,91</t>
+          <t>50,04; 62,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53,28; 65,56</t>
+          <t>53,55; 65,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50,29; 64,88</t>
+          <t>47,64; 58,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,14; 33,45</t>
+          <t>22,33; 34,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 39,95</t>
+          <t>28,54; 40,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,92; 40,05</t>
+          <t>29,26; 40,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,21; 36,57</t>
+          <t>26,97; 35,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>35,41; 43,9</t>
+          <t>35,55; 44,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41,14; 50,01</t>
+          <t>40,51; 49,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,51; 52,38</t>
+          <t>42,88; 51,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,18; 49,18</t>
+          <t>38,41; 46,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,07; 47,23</t>
+          <t>38,05; 47,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,07; 61,56</t>
+          <t>52,8; 61,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,37; 55,99</t>
+          <t>46,99; 55,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,7; 55,38</t>
+          <t>43,43; 54,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 14,83</t>
+          <t>8,75; 15,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,22; 28,21</t>
+          <t>20,34; 28,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 21,78</t>
+          <t>14,93; 21,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,53; 26,92</t>
+          <t>19,29; 26,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 29,62</t>
+          <t>24,09; 29,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,73; 43,18</t>
+          <t>37,06; 43,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,11; 37,42</t>
+          <t>31,45; 37,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>33,12; 39,82</t>
+          <t>32,14; 38,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,9; 64,75</t>
+          <t>53,69; 64,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,51; 62,85</t>
+          <t>51,72; 63,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,07; 67,24</t>
+          <t>55,95; 66,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53,09; 64,14</t>
+          <t>54,21; 64,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,17; 29,87</t>
+          <t>20,23; 29,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,25; 38,17</t>
+          <t>27,08; 37,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,83; 40,22</t>
+          <t>29,61; 40,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,7; 30,1</t>
+          <t>20,69; 28,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,9; 45,49</t>
+          <t>38,16; 45,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40,43; 48,42</t>
+          <t>40,54; 48,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43,6; 51,3</t>
+          <t>43,84; 51,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,82; 45,05</t>
+          <t>37,79; 44,49</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59,71; 70,0</t>
+          <t>60,13; 70,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,42; 52,25</t>
+          <t>41,83; 52,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,92; 64,2</t>
+          <t>53,82; 64,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,84; 63,88</t>
+          <t>47,76; 61,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 39,01</t>
+          <t>30,38; 39,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,01; 23,0</t>
+          <t>14,89; 22,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 41,09</t>
+          <t>31,0; 41,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,5; 33,8</t>
+          <t>28,6; 37,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46,11; 53,0</t>
+          <t>45,93; 53,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,94; 36,02</t>
+          <t>28,7; 35,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43,38; 50,72</t>
+          <t>43,59; 51,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 44,23</t>
+          <t>38,81; 47,14</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,11; 49,44</t>
+          <t>36,07; 49,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>50,21; 64,23</t>
+          <t>49,68; 63,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,99; 48,72</t>
+          <t>34,76; 48,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,9; 22,77</t>
+          <t>12,69; 22,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 23,8</t>
+          <t>13,03; 24,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,51; 27,59</t>
+          <t>16,85; 27,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,27; 22,52</t>
+          <t>12,58; 22,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,02</t>
+          <t>2,77; 7,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,85; 35,1</t>
+          <t>25,9; 35,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,39; 44,1</t>
+          <t>34,56; 43,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,77; 33,33</t>
+          <t>24,7; 32,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,88</t>
+          <t>8,19; 13,41</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,24; 76,05</t>
+          <t>65,33; 76,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,44; 71,06</t>
+          <t>58,89; 71,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64,75; 76,11</t>
+          <t>64,3; 75,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,93; 66,14</t>
+          <t>54,84; 65,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,25; 45,26</t>
+          <t>32,84; 44,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,2; 35,35</t>
+          <t>24,32; 35,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,53; 43,4</t>
+          <t>32,14; 43,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,57; 42,32</t>
+          <t>32,28; 42,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50,7; 58,97</t>
+          <t>50,72; 59,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42,74; 51,46</t>
+          <t>42,97; 51,06</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49,07; 57,86</t>
+          <t>49,52; 57,91</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46,32; 53,94</t>
+          <t>45,66; 52,92</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,94; 49,51</t>
+          <t>41,04; 48,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,45; 60,94</t>
+          <t>52,85; 61,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,47; 61,64</t>
+          <t>53,83; 61,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44,94; 55,28</t>
+          <t>44,41; 53,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,76; 22,86</t>
+          <t>16,72; 23,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,03; 31,2</t>
+          <t>23,85; 31,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,73; 40,35</t>
+          <t>32,89; 40,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29,37; 73,86</t>
+          <t>27,72; 34,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,46; 34,81</t>
+          <t>29,29; 34,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38,65; 44,37</t>
+          <t>38,54; 44,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43,86; 49,36</t>
+          <t>43,87; 49,58</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,06; 67,92</t>
+          <t>37,04; 42,23</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,84; 66,95</t>
+          <t>59,71; 66,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,62; 58,33</t>
+          <t>50,9; 58,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52,59; 59,83</t>
+          <t>52,41; 59,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,57; 42,19</t>
+          <t>35,58; 42,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,39; 30,76</t>
+          <t>24,14; 30,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,73; 26,17</t>
+          <t>19,75; 26,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,8; 33,53</t>
+          <t>26,75; 33,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,01; 16,58</t>
+          <t>11,78; 16,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42,34; 47,2</t>
+          <t>42,06; 47,35</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35,42; 40,48</t>
+          <t>35,66; 40,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39,91; 45,12</t>
+          <t>40,14; 45,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,9; 27,84</t>
+          <t>24,33; 28,85</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52,95; 56,69</t>
+          <t>53,22; 56,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54,31; 58,04</t>
+          <t>54,21; 57,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55,34; 58,84</t>
+          <t>55,33; 58,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>34,76; 49,91</t>
+          <t>45,81; 49,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,1; 26,05</t>
+          <t>22,97; 25,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,24</t>
+          <t>24,27; 27,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,13; 32,39</t>
+          <t>29,16; 32,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23,29; 41,57</t>
+          <t>23,07; 25,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,25; 40,71</t>
+          <t>38,1; 40,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39,16; 41,7</t>
+          <t>39,14; 41,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42,4; 44,83</t>
+          <t>42,29; 44,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,22</t>
+          <t>34,4; 36,83</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169898</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>121382; 153586</t>
+          <t>122970; 152897</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148601; 181898</t>
+          <t>147017; 182480</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>153539; 188911</t>
+          <t>154302; 188083</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156628; 202056</t>
+          <t>151895; 187626</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57539; 86926</t>
+          <t>58016; 88593</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79626; 113102</t>
+          <t>80818; 113960</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81284; 112584</t>
+          <t>82257; 114723</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78805; 105927</t>
+          <t>85226; 111371</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>187223; 232070</t>
+          <t>187962; 233194</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>237372; 288520</t>
+          <t>233706; 286294</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>247652; 298170</t>
+          <t>244085; 295561</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>241485; 295637</t>
+          <t>243869; 292093</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>184246; 228591</t>
+          <t>184140; 227783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>249165; 294617</t>
+          <t>252674; 295171</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>232311; 274598</t>
+          <t>230452; 274058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>230715; 285870</t>
+          <t>229495; 287587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44110; 73963</t>
+          <t>43652; 75145</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>102437; 142866</t>
+          <t>103005; 141849</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76169; 112459</t>
+          <t>77087; 112752</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100478; 138486</t>
+          <t>105301; 142385</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>235736; 291096</t>
+          <t>236748; 290925</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>361832; 425377</t>
+          <t>365056; 428294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313180; 376730</t>
+          <t>316660; 380304</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>341280; 410364</t>
+          <t>345279; 416114</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88779</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>274998</t>
+          <t>276092</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>169281; 203367</t>
+          <t>168607; 203698</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>156893; 191424</t>
+          <t>157518; 193738</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168888; 198973</t>
+          <t>165554; 198135</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>167807; 202714</t>
+          <t>171303; 204239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>67258; 99598</t>
+          <t>67461; 99494</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90198; 126353</t>
+          <t>89662; 125091</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98555; 132895</t>
+          <t>97817; 134987</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75668; 104955</t>
+          <t>73651; 102452</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>245416; 294554</t>
+          <t>247080; 295901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>257020; 307747</t>
+          <t>257717; 308687</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>273092; 321298</t>
+          <t>274542; 323018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>251384; 299450</t>
+          <t>253931; 298964</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>178179</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>124346</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341803</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>211820; 248337</t>
+          <t>213310; 248564</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>148223; 186973</t>
+          <t>149679; 188751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>194343; 231399</t>
+          <t>193982; 231854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155779; 199656</t>
+          <t>178207; 227896</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110103; 144909</t>
+          <t>112851; 146431</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57701; 88399</t>
+          <t>57254; 88374</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115685; 155493</t>
+          <t>117281; 155793</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78486; 160776</t>
+          <t>120686; 157660</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>334877; 384854</t>
+          <t>333564; 386195</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>214792; 267347</t>
+          <t>213059; 265631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>320490; 374748</t>
+          <t>322082; 377324</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>218925; 348665</t>
+          <t>308576; 374845</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>71538; 97940</t>
+          <t>71459; 98361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>106765; 136572</t>
+          <t>105637; 136000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72603; 101095</t>
+          <t>72139; 100449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23058; 40705</t>
+          <t>26100; 45515</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27002; 49199</t>
+          <t>26934; 51149</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36244; 60588</t>
+          <t>36992; 61204</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26829; 49220</t>
+          <t>27494; 49297</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5081; 14655</t>
+          <t>6298; 17580</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104641; 142056</t>
+          <t>104831; 141671</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148628; 190609</t>
+          <t>149363; 189103</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105565; 142033</t>
+          <t>105236; 140181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30427; 49889</t>
+          <t>35433; 58055</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164637</t>
+          <t>162549</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>261057</t>
+          <t>260743</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>175367; 204432</t>
+          <t>175605; 204332</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>156923; 187613</t>
+          <t>155471; 188862</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>167306; 196653</t>
+          <t>166138; 195932</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>150145; 177563</t>
+          <t>147803; 175679</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91782; 124950</t>
+          <t>90672; 122469</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67005; 97887</t>
+          <t>67333; 98246</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85493; 117688</t>
+          <t>87150; 116842</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>83726; 108778</t>
+          <t>85150; 111469</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>276260; 321321</t>
+          <t>276368; 323621</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>231220; 278377</t>
+          <t>232427; 276222</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>259823; 306412</t>
+          <t>262199; 306636</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>243416; 283455</t>
+          <t>243491; 282206</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308093</t>
+          <t>350886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>401553</t>
+          <t>236397</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>709646</t>
+          <t>587283</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>247681; 299507</t>
+          <t>248293; 296307</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>331430; 385070</t>
+          <t>333991; 386977</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>342632; 394955</t>
+          <t>344926; 394174</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>279054; 343235</t>
+          <t>317608; 380139</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>106197; 144864</t>
+          <t>105928; 146481</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>164624; 213725</t>
+          <t>163375; 212959</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>223801; 275906</t>
+          <t>224864; 277345</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>248222; 624290</t>
+          <t>212566; 261072</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>364903; 431173</t>
+          <t>362763; 431264</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>508986; 584383</t>
+          <t>507581; 580956</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>580950; 653802</t>
+          <t>581003; 656629</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>572588; 995784</t>
+          <t>548999; 625933</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>442313; 494858</t>
+          <t>441310; 491696</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>370140; 426544</t>
+          <t>372217; 427906</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>392310; 446307</t>
+          <t>390964; 445555</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>126052; 391844</t>
+          <t>283955; 342689</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>190344; 240019</t>
+          <t>188394; 239027</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>157750; 209241</t>
+          <t>157902; 208024</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>216647; 271026</t>
+          <t>216264; 270639</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>85630; 118234</t>
+          <t>97577; 136834</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>643290; 717220</t>
+          <t>639010; 719489</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>542170; 619588</t>
+          <t>545789; 619431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>620300; 701349</t>
+          <t>623876; 700095</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>211748; 457055</t>
+          <t>395615; 469126</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1580302</t>
+          <t>1682411</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1028192</t>
+          <t>907649</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2608494</t>
+          <t>2590061</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1711533; 1832417</t>
+          <t>1720474; 1832180</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1778373; 1900727</t>
+          <t>1775043; 1894175</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1819409; 1934282</t>
+          <t>1819001; 1933753</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1200308; 1723251</t>
+          <t>1614562; 1751951</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>776264; 875351</t>
+          <t>771836; 872284</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>846842; 949519</t>
+          <t>846100; 953775</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1016079; 1129875</t>
+          <t>1017218; 1127265</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>850746; 1518369</t>
+          <t>859504; 958057</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2521776; 2683702</t>
+          <t>2512024; 2675544</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2647611; 2819507</t>
+          <t>2645986; 2819861</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2873027; 3037583</t>
+          <t>2865621; 3032254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2351846; 3000156</t>
+          <t>2494475; 2670491</t>
         </is>
       </c>
     </row>
